--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96457</v>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96458</v>
+        <v>96460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96460</v>
+        <v>96464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96464</v>
+        <v>96465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96469</v>
+        <v>96471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125821021</v>
       </c>
       <c r="B3" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125821022</v>
       </c>
       <c r="B2" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -876,6 +876,107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130816868</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97090</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sillerforsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>526945</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6929655</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>130816868</v>
       </c>
       <c r="B4" t="n">
-        <v>97090</v>
+        <v>97093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48374-2024 artfynd.xlsx
+++ b/artfynd/A 48374-2024 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>130816868</v>
       </c>
       <c r="B4" t="n">
-        <v>97093</v>
+        <v>97102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
